--- a/data/dividends_info_20260802.xlsx
+++ b/data/dividends_info_20260802.xlsx
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4.119999885559082</v>
+        <v>4.130000114440918</v>
       </c>
       <c r="I25" t="n">
-        <v>3.398058346814786</v>
+        <v>3.38983041454351</v>
       </c>
       <c r="J25" t="n">
         <v>-13</v>
@@ -3576,44 +3576,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Itway S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>